--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486404_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486404_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0604</v>
+        <v>6.7821</v>
       </c>
       <c r="E2" t="n">
-        <v>4.8614</v>
+        <v>4.7064</v>
       </c>
       <c r="F2" t="n">
-        <v>2.199</v>
+        <v>2.0757</v>
       </c>
       <c r="G2" t="n">
         <v>3.798</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7828</v>
+        <v>1.5045</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8736</v>
+        <v>0.7186</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9092</v>
+        <v>0.7859</v>
       </c>
       <c r="V2" t="n">
         <v>0.1745</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.1839</v>
+        <v>5.3853</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9577</v>
+        <v>4.4674</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2261</v>
+        <v>0.9179</v>
       </c>
       <c r="G3" t="n">
         <v>2.5897</v>
@@ -688,13 +688,13 @@
         <v>0.6525</v>
       </c>
       <c r="S3" t="n">
-        <v>2.139</v>
+        <v>1.3405</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3087</v>
+        <v>0.8184</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8304</v>
+        <v>0.5221</v>
       </c>
       <c r="V3" t="n">
         <v>1.8902</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. CREMO</t>
+          <t>D. CUEVAS SIMARRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,31 +721,31 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.9459</v>
+        <v>4.611</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8384</v>
+        <v>3.3939</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1075</v>
+        <v>1.2171</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4766</v>
+        <v>2.6667</v>
       </c>
       <c r="H4" t="n">
-        <v>-3.1173</v>
+        <v>-1.3535</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5939</v>
+        <v>4.0202</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4944</v>
+        <v>3.6845</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.5234</v>
+        <v>0.2404</v>
       </c>
       <c r="L4" t="n">
-        <v>4.0178</v>
+        <v>3.4441</v>
       </c>
       <c r="M4" t="n">
         <v>-1.0178</v>
@@ -757,37 +757,37 @@
         <v>0.5760999999999999</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2175</v>
+        <v>-0.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R4" t="n">
         <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3171</v>
+        <v>1.2939</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3016</v>
+        <v>0.3641</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0154</v>
+        <v>0.9298</v>
       </c>
       <c r="V4" t="n">
-        <v>0.9347</v>
+        <v>1.5204</v>
       </c>
       <c r="W4" t="n">
-        <v>1.13</v>
+        <v>1.5204</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. CUEVAS SIMARRO</t>
+          <t>J. CREMO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,31 +799,31 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.6494</v>
+        <v>4.1947</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5864</v>
+        <v>3.0872</v>
       </c>
       <c r="F5" t="n">
-        <v>1.063</v>
+        <v>1.1075</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6667</v>
+        <v>1.4766</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.3535</v>
+        <v>-3.1173</v>
       </c>
       <c r="I5" t="n">
-        <v>4.0202</v>
+        <v>4.5939</v>
       </c>
       <c r="J5" t="n">
-        <v>3.6845</v>
+        <v>2.4944</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2404</v>
+        <v>-1.5234</v>
       </c>
       <c r="L5" t="n">
-        <v>3.4441</v>
+        <v>4.0178</v>
       </c>
       <c r="M5" t="n">
         <v>-1.0178</v>
@@ -835,31 +835,31 @@
         <v>0.5760999999999999</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.87</v>
+        <v>0.2175</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R5" t="n">
         <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3323</v>
+        <v>1.5658</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4434</v>
+        <v>0.5504</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7756999999999999</v>
+        <v>1.0154</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5204</v>
+        <v>0.9347</v>
       </c>
       <c r="W5" t="n">
-        <v>1.5204</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4337</v>
+        <v>3.3182</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6892</v>
+        <v>1.9127</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7445</v>
+        <v>1.4055</v>
       </c>
       <c r="G6" t="n">
         <v>1.4642</v>
@@ -922,13 +922,13 @@
         <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5344</v>
+        <v>1.4189</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6201</v>
+        <v>0.8436</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9144</v>
+        <v>0.5753</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9261</v>
+        <v>2.4771</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5007</v>
+        <v>0.836</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4254</v>
+        <v>1.6411</v>
       </c>
       <c r="G7" t="n">
         <v>1.1232</v>
@@ -1000,13 +1000,13 @@
         <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7158</v>
+        <v>1.2669</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4266</v>
+        <v>0.7619</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2892</v>
+        <v>0.505</v>
       </c>
       <c r="V7" t="n">
         <v>0.7395</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0763</v>
+        <v>1.3867</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4326</v>
+        <v>2.6813</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3562</v>
+        <v>-1.2946</v>
       </c>
       <c r="G8" t="n">
         <v>1.6023</v>
@@ -1078,13 +1078,13 @@
         <v>0.435</v>
       </c>
       <c r="S8" t="n">
-        <v>0.6492</v>
+        <v>0.9596</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2776</v>
+        <v>0.5264</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3716</v>
+        <v>0.4332</v>
       </c>
       <c r="V8" t="n">
         <v>0.5649999999999999</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. DIOP GAYE</t>
+          <t>A. THIAM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6882</v>
+        <v>0.1637</v>
       </c>
       <c r="E9" t="n">
-        <v>1.2197</v>
+        <v>-0.9236</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5315</v>
+        <v>1.0873</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9103</v>
+        <v>-2.6318</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1734</v>
+        <v>-3.1776</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0838</v>
+        <v>0.5458</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1611</v>
+        <v>-2.046</v>
       </c>
       <c r="K9" t="n">
-        <v>1.1378</v>
+        <v>-2.3137</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2989</v>
+        <v>0.2677</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7493</v>
+        <v>-0.5858</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9643</v>
+        <v>-0.8639</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.7849</v>
+        <v>0.2781</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S9" t="n">
-        <v>4.1413</v>
+        <v>2.0985</v>
       </c>
       <c r="T9" t="n">
-        <v>2.4683</v>
+        <v>1.1224</v>
       </c>
       <c r="U9" t="n">
-        <v>1.673</v>
+        <v>0.9761</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3252</v>
+        <v>-0.3904</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3252</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. THIAM</t>
+          <t>P. JORGENSEN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2696</v>
+        <v>-0.3792</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7252999999999999</v>
+        <v>-0.9216</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9949</v>
+        <v>0.5423</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.6318</v>
+        <v>-3.4034</v>
       </c>
       <c r="H10" t="n">
-        <v>-3.1776</v>
+        <v>-1.8551</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5458</v>
+        <v>-1.5483</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.046</v>
+        <v>-3.2112</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.3137</v>
+        <v>-1.7028</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2677</v>
+        <v>-1.5084</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5858</v>
+        <v>-0.1922</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8639</v>
+        <v>-0.1523</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2781</v>
+        <v>-0.0399</v>
       </c>
       <c r="P10" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S10" t="n">
-        <v>2.2043</v>
+        <v>1.4592</v>
       </c>
       <c r="T10" t="n">
-        <v>1.3207</v>
+        <v>1.1596</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8836000000000001</v>
+        <v>0.2995</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3904</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X10" t="n">
         <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.3904</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. BRAZ</t>
+          <t>C. DE SOUZA PACHECO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1388</v>
+        <v>-0.5703</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.9443</v>
+        <v>-0.6366000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1945</v>
+        <v>0.0663</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9812</v>
+        <v>-0.1921</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9732</v>
+        <v>-1.11</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.008</v>
+        <v>0.918</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.6138</v>
+        <v>0.0001</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6903</v>
+        <v>-0.9577</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0765</v>
+        <v>0.9578</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3674</v>
+        <v>-0.1922</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2829</v>
+        <v>-0.1523</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.08450000000000001</v>
+        <v>-0.0399</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0875</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.435</v>
       </c>
       <c r="S11" t="n">
-        <v>0.93</v>
+        <v>1.1873</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7571</v>
+        <v>0.9734</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1729</v>
+        <v>0.2139</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.1745</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. JORGENSEN</t>
+          <t>I. DIOP GAYE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.2338</v>
+        <v>-1.0707</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4371</v>
+        <v>0.0156</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2033</v>
+        <v>-1.0863</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.4034</v>
+        <v>-1.9103</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.8551</v>
+        <v>0.1734</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.5483</v>
+        <v>-2.0838</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.2112</v>
+        <v>-0.1611</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.7028</v>
+        <v>1.1378</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.5084</v>
+        <v>-1.2989</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1922</v>
+        <v>-1.7493</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1523</v>
+        <v>-0.9643</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0399</v>
+        <v>-0.7849</v>
       </c>
       <c r="P12" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q12" t="n">
+        <v>-1.0875</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.3824</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.2642</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.1182</v>
+      </c>
+      <c r="V12" t="n">
+        <v>-1.3252</v>
+      </c>
+      <c r="W12" t="n">
         <v>0</v>
       </c>
-      <c r="R12" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.6046</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0.6441</v>
-      </c>
-      <c r="U12" t="n">
-        <v>-0.0395</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.13</v>
-      </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.3252</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C. DE SOUZA PACHECO</t>
+          <t>M. BRAZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.1378</v>
+        <v>-1.5481</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.7109</v>
+        <v>-1.3228</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4269</v>
+        <v>-0.2253</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.1921</v>
+        <v>-0.9812</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.11</v>
+        <v>-0.9732</v>
       </c>
       <c r="I13" t="n">
-        <v>0.918</v>
+        <v>-0.008</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0001</v>
+        <v>-0.6138</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.9577</v>
+        <v>-0.6903</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9578</v>
+        <v>0.0765</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1922</v>
+        <v>-0.3674</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.1523</v>
+        <v>-0.2829</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.0399</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.7401</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R13" t="n">
-        <v>0.435</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3802</v>
+        <v>0.5206</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1009</v>
+        <v>0.3785</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2793</v>
+        <v>0.1421</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1745</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3904</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>23.7231</v>
+        <v>24.7505</v>
       </c>
       <c r="E14" t="n">
-        <v>16.2685</v>
+        <v>17.29589999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>7.454599999999999</v>
+        <v>7.4545</v>
       </c>
       <c r="G14" t="n">
-        <v>5.601900000000002</v>
+        <v>5.601900000000001</v>
       </c>
       <c r="H14" t="n">
         <v>-7.785300000000001</v>
@@ -1522,19 +1522,19 @@
         <v>11.6517</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9457999999999986</v>
+        <v>0.9457999999999992</v>
       </c>
       <c r="L14" t="n">
         <v>10.7059</v>
       </c>
       <c r="M14" t="n">
-        <v>-6.049899999999999</v>
+        <v>-6.0499</v>
       </c>
       <c r="N14" t="n">
         <v>-8.731</v>
       </c>
       <c r="O14" t="n">
-        <v>2.681200000000001</v>
+        <v>2.6812</v>
       </c>
       <c r="P14" t="n">
         <v>-3.2627</v>
@@ -1543,19 +1543,19 @@
         <v>-11.9628</v>
       </c>
       <c r="R14" t="n">
-        <v>8.700000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>15.9706</v>
+        <v>16.9981</v>
       </c>
       <c r="T14" t="n">
-        <v>8.454100000000002</v>
+        <v>9.4815</v>
       </c>
       <c r="U14" t="n">
-        <v>7.5166</v>
+        <v>7.516500000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>5.413200000000001</v>
+        <v>5.4132</v>
       </c>
       <c r="W14" t="n">
         <v>8.1258</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5899</v>
+        <v>1.908</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3385</v>
+        <v>1.2267</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2514</v>
+        <v>0.6812</v>
       </c>
       <c r="G15" t="n">
         <v>1.9825</v>
@@ -1624,13 +1624,13 @@
         <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0477</v>
+        <v>-0.6342</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9673</v>
+        <v>-1.0791</v>
       </c>
       <c r="U15" t="n">
-        <v>1.015</v>
+        <v>0.4449</v>
       </c>
       <c r="V15" t="n">
         <v>1.2122</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.664</v>
+        <v>-0.3558</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9692</v>
+        <v>1.5222</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.6332</v>
+        <v>-1.878</v>
       </c>
       <c r="G16" t="n">
         <v>0.9454</v>
@@ -1702,13 +1702,13 @@
         <v>0.6525</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.132</v>
+        <v>-0.8238</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0649</v>
+        <v>-0.5119</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.0671</v>
+        <v>-0.3118</v>
       </c>
       <c r="V16" t="n">
         <v>-1.13</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2056</v>
+        <v>-0.5929</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3951</v>
+        <v>2.2833</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.6007</v>
+        <v>-2.8762</v>
       </c>
       <c r="G17" t="n">
         <v>2.4139</v>
@@ -1780,13 +1780,13 @@
         <v>1.305</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.3771</v>
+        <v>-1.7644</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9553</v>
+        <v>-1.0671</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.4217</v>
+        <v>-0.6973</v>
       </c>
       <c r="V17" t="n">
         <v>-2.5475</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. SIQUIER COSTA</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6979</v>
+        <v>-1.0225</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7596</v>
+        <v>0.1934</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0617</v>
+        <v>-1.2159</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.5215</v>
+        <v>0.0378</v>
       </c>
       <c r="H18" t="n">
-        <v>0.52</v>
+        <v>1.32</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.0415</v>
+        <v>-1.2822</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.4171</v>
+        <v>1.627</v>
       </c>
       <c r="K18" t="n">
-        <v>0.073</v>
+        <v>1.7218</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4901</v>
+        <v>-0.0948</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1044</v>
+        <v>-1.5891</v>
       </c>
       <c r="N18" t="n">
-        <v>0.447</v>
+        <v>-0.4018</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5514</v>
+        <v>-1.1873</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6525</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.305</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8289</v>
+        <v>-1.4078</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3425</v>
+        <v>-1.0839</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4864</v>
+        <v>-0.3239</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.3904</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>J. BOCCA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8035</v>
+        <v>-1.1829</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1934</v>
+        <v>0.5447</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9969</v>
+        <v>-1.7276</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0378</v>
+        <v>-0.156</v>
       </c>
       <c r="H19" t="n">
-        <v>1.32</v>
+        <v>0.1397</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2822</v>
+        <v>-0.2957</v>
       </c>
       <c r="J19" t="n">
-        <v>1.627</v>
+        <v>1.8356</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7218</v>
+        <v>0.0944</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0948</v>
+        <v>1.7412</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.5891</v>
+        <v>-1.9916</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4018</v>
+        <v>0.0452</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1873</v>
+        <v>-2.0368</v>
       </c>
       <c r="P19" t="n">
+        <v>2.1751</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.2175</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.305</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.0875</v>
+        <v>2.3926</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.1888</v>
+        <v>-1.7845</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0839</v>
+        <v>-0.8989</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1048</v>
+        <v>-0.8857</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5649999999999999</v>
+        <v>-1.4175</v>
       </c>
       <c r="W19" t="n">
-        <v>0.9554</v>
+        <v>-0.1745</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3904</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. BOCCA</t>
+          <t>O. SIQUIER COSTA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3493</v>
+        <v>-1.5245</v>
       </c>
       <c r="E20" t="n">
-        <v>0.09760000000000001</v>
+        <v>-1.6478</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4469</v>
+        <v>0.1233</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.156</v>
+        <v>-1.5215</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1397</v>
+        <v>0.52</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2957</v>
+        <v>-2.0415</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8356</v>
+        <v>-1.4171</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0944</v>
+        <v>0.073</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7412</v>
+        <v>-1.4901</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9916</v>
+        <v>-0.1044</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0452</v>
+        <v>0.447</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.0368</v>
+        <v>-0.5514</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1751</v>
+        <v>0.6525</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3926</v>
+        <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.9509</v>
+        <v>-0.6555</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3459</v>
+        <v>-0.2307</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.605</v>
+        <v>-0.4248</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4175</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.1745</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.3764</v>
+        <v>-5.1939</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3849</v>
+        <v>-2.6085</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9915</v>
+        <v>-2.5855</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6398</v>
@@ -2092,13 +2092,13 @@
         <v>1.9576</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.0586</v>
+        <v>-1.8761</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8063</v>
+        <v>-1.0298</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2523</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-1.243</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>O. MATULIONIS</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.5564</v>
+        <v>-5.4138</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.6278</v>
+        <v>-4.4525</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9286</v>
+        <v>-0.9613</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2598</v>
+        <v>-5.4044</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2039</v>
+        <v>-0.0305</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.0559</v>
+        <v>-5.374</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.7696</v>
+        <v>-3.5818</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0516</v>
+        <v>0.3713</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.718</v>
+        <v>-3.9532</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4902</v>
+        <v>-1.8226</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1523</v>
+        <v>-0.4018</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.3379</v>
+        <v>-1.4208</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.5225</v>
+        <v>1.305</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1751</v>
+        <v>-0.2175</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7264</v>
+        <v>-1.5096</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8784</v>
+        <v>-0.8484</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8479</v>
+        <v>-0.6612</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0477</v>
+        <v>0.1952</v>
       </c>
       <c r="W22" t="n">
         <v>0.1952</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.243</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>O. MATULIONIS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.6598</v>
+        <v>-5.8744</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.676</v>
+        <v>-4.5161</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.9838</v>
+        <v>-1.3583</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.4044</v>
+        <v>-2.2598</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0305</v>
+        <v>-0.2039</v>
       </c>
       <c r="I23" t="n">
-        <v>-5.374</v>
+        <v>-2.0559</v>
       </c>
       <c r="J23" t="n">
-        <v>-3.5818</v>
+        <v>-1.7696</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3713</v>
+        <v>-0.0516</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.9532</v>
+        <v>-1.718</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8226</v>
+        <v>-0.4902</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4018</v>
+        <v>-0.1523</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.4208</v>
+        <v>-0.3379</v>
       </c>
       <c r="P23" t="n">
-        <v>1.305</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2175</v>
+        <v>-2.1751</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.7556</v>
+        <v>-1.0443</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0719</v>
+        <v>-0.7667</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.6837</v>
+        <v>-0.2776</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1952</v>
+        <v>-1.0477</v>
       </c>
       <c r="W23" t="n">
         <v>0.1952</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.243</v>
       </c>
     </row>
     <row r="24">
@@ -2281,16 +2281,16 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-23.723</v>
+        <v>-19.2527</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.454499999999999</v>
+        <v>-7.454599999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.2685</v>
+        <v>-11.7983</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.601899999999999</v>
+        <v>-5.601900000000001</v>
       </c>
       <c r="H24" t="n">
         <v>7.7854</v>
@@ -2299,19 +2299,19 @@
         <v>-13.3874</v>
       </c>
       <c r="J24" t="n">
-        <v>6.049799999999999</v>
+        <v>6.049800000000001</v>
       </c>
       <c r="K24" t="n">
         <v>8.7309</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.681299999999999</v>
+        <v>-2.6813</v>
       </c>
       <c r="M24" t="n">
         <v>-11.6516</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9457</v>
+        <v>-0.9456999999999999</v>
       </c>
       <c r="O24" t="n">
         <v>-10.706</v>
@@ -2320,19 +2320,19 @@
         <v>3.2626</v>
       </c>
       <c r="Q24" t="n">
-        <v>-8.7003</v>
+        <v>-8.700299999999999</v>
       </c>
       <c r="R24" t="n">
         <v>11.9628</v>
       </c>
       <c r="S24" t="n">
-        <v>-15.9706</v>
+        <v>-11.5002</v>
       </c>
       <c r="T24" t="n">
-        <v>-7.5164</v>
+        <v>-7.516500000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-8.453900000000001</v>
+        <v>-3.9837</v>
       </c>
       <c r="V24" t="n">
         <v>-5.4133</v>
